--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46282.74069199422</v>
+        <v>46282.78242527427</v>
       </c>
     </row>
     <row r="4">
@@ -793,7 +793,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
@@ -986,24 +986,24 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>33.95999908</v>
+        <v>34.88000107</v>
       </c>
       <c r="H2" t="n">
-        <v>33.95999908</v>
+        <v>34.88000107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254); E - %69.8 (n=212); G - %68.8 (n=208)</t>
+          <t>B - %75.2 (n=254); E - %69.8 (n=212); L - %68.1 (n=364)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-1.508122003878654</v>
+        <v>1.160097260256521</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1176497647058738</v>
+        <v>2.58823844117646</v>
       </c>
       <c r="L2" t="n">
-        <v>2.971496524162776</v>
+        <v>5.761072033053138</v>
       </c>
       <c r="M2" t="n">
         <v>2030</v>
@@ -1084,24 +1084,24 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11.09</v>
+        <v>11.11999989</v>
       </c>
       <c r="H3" t="n">
-        <v>11.09</v>
+        <v>11.11999989</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254); E - %69.8 (n=212)</t>
+          <t>B - %75.2 (n=254); E - %69.8 (n=212); L - %68.1 (n=364)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-1.352569867218989e-06</v>
+        <v>0.2705116284421383</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.204586831508992</v>
+        <v>-1.940037540475681</v>
       </c>
       <c r="L3" t="n">
-        <v>4.229319977634516</v>
+        <v>4.511273822008177</v>
       </c>
       <c r="M3" t="n">
         <v>2030</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>109.1</v>
+        <v>109.5</v>
       </c>
       <c r="H4" t="n">
-        <v>109.1</v>
+        <v>109.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-3.621905530448877</v>
+        <v>-3.268548630468848</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.432245770508893</v>
+        <v>-6.089192592765569</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.327660717093694</v>
+        <v>-1.969558648228775</v>
       </c>
       <c r="M4" t="n">
         <v>2030</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>89.8</v>
+        <v>89.75</v>
       </c>
       <c r="H5" t="n">
-        <v>89.8</v>
+        <v>89.75</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-4.822467984932444</v>
+        <v>-4.875462156433041</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.374079502398931</v>
+        <v>-5.426766540537898</v>
       </c>
       <c r="L5" t="n">
-        <v>1.069219523195342</v>
+        <v>1.012944902079971</v>
       </c>
       <c r="M5" t="n">
         <v>649</v>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>380</v>
+        <v>379.75</v>
       </c>
       <c r="H6" t="n">
-        <v>380</v>
+        <v>379.75</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2.013422818791955</v>
+        <v>1.946308724832213</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.642409033877037</v>
+        <v>-4.70514429109159</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06574621959237748</v>
+        <v>-0.1314924391847438</v>
       </c>
       <c r="M6" t="n">
         <v>2030</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H7" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-3.003663003663004</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.03264726756565</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.779069767441856</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="M7" t="n">
         <v>2030</v>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Morning Star</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1570,73 +1570,69 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>80.45</v>
+        <v>666</v>
       </c>
       <c r="H8" t="n">
-        <v>80.45</v>
+        <v>666</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254); E - %69.8 (n=212)</t>
+          <t>B - %75.2 (n=254)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.2479870132743867</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="K8" t="n">
-        <v>1.19496855345913</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="L8" t="n">
-        <v>2.093904677837455</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="M8" t="n">
-        <v>2030</v>
+        <v>930</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.6876847290640394</v>
+        <v>0.6559139784946236</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.680327868852459</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>2027</v>
+        <v>928</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.7636901825357671</v>
+        <v>0.7575431034482759</v>
       </c>
       <c r="W8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.7786885245901639</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1649,17 +1645,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Piercing Line</t>
+          <t>Bullish Engulfing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1668,69 +1664,73 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20.94</v>
+        <v>80.40000153</v>
       </c>
       <c r="H9" t="n">
-        <v>20.94</v>
+        <v>80.40000153</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254)</t>
+          <t>B - %75.2 (n=254); E - %69.8 (n=212)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-3.679851786861355</v>
+        <v>-0.3099813952353148</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.234747734436039</v>
+        <v>1.132077396226405</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.240896723656782</v>
+        <v>2.030454845267915</v>
       </c>
       <c r="M9" t="n">
-        <v>649</v>
+        <v>2030</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.662557781201849</v>
+        <v>0.6876847290640394</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.680327868852459</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U9" t="n">
-        <v>649</v>
+        <v>2027</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.7596302003081664</v>
+        <v>0.7636901825357671</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="Y9" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>63.95</v>
+        <v>64.30000305</v>
       </c>
       <c r="H10" t="n">
-        <v>63.95</v>
+        <v>64.30000305</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-7.919362406825847</v>
+        <v>-7.41539830981951</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.68435563333888</v>
+        <v>-10.1955245474742</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.642857142857141</v>
+        <v>-8.142852785714283</v>
       </c>
       <c r="M10" t="n">
         <v>649</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>132.9</v>
+        <v>132.5</v>
       </c>
       <c r="H11" t="n">
-        <v>132.9</v>
+        <v>132.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-0.7468214679283824</v>
+        <v>-1.045551877355233</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3748080381283936</v>
+        <v>-0.6746581268022078</v>
       </c>
       <c r="L11" t="n">
-        <v>1.141557206723731</v>
+        <v>0.837143189547751</v>
       </c>
       <c r="M11" t="n">
         <v>2030</v>
@@ -1954,20 +1954,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.97</v>
+        <v>0.97000003</v>
       </c>
       <c r="H12" t="n">
-        <v>0.97</v>
+        <v>0.97000003</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.901958919646243</v>
+        <v>-4.901955978469719</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="M12" t="n">
         <v>2413</v>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13.44</v>
+        <v>13.36999989</v>
       </c>
       <c r="H13" t="n">
-        <v>13.44</v>
+        <v>13.36999989</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2055,62 +2055,58 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-2.890174462895512</v>
+        <v>-3.395955599032263</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.183404476141426</v>
+        <v>-2.692866711743769</v>
       </c>
       <c r="L13" t="n">
-        <v>3.783785306480247</v>
+        <v>3.243243908588145</v>
       </c>
       <c r="M13" t="n">
-        <v>2030</v>
+        <v>649</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6876847290640394</v>
+        <v>0.662557781201849</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="Q13" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.680327868852459</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>2027</v>
+        <v>649</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.7636901825357671</v>
+        <v>0.7596302003081664</v>
       </c>
       <c r="W13" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="X13" s="4" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z13" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y13" t="n">
-        <v>122</v>
-      </c>
-      <c r="Z13" s="4" t="n">
-        <v>0.7786885245901639</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2142,24 +2138,24 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35.02</v>
+        <v>34.72000122</v>
       </c>
       <c r="H14" t="n">
-        <v>35.02</v>
+        <v>34.72000122</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254); E - %69.8 (n=212); L - %68.1 (n=364)</t>
+          <t>B - %75.2 (n=254); E - %69.8 (n=212)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.1716273500542709</v>
+        <v>-0.6864927526193831</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.396881394518857</v>
+        <v>-3.232998370699325</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.129300368905117</v>
+        <v>-1.976276076131711</v>
       </c>
       <c r="M14" t="n">
         <v>2030</v>
@@ -2226,12 +2222,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2240,10 +2236,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>220</v>
+        <v>218.69999695</v>
       </c>
       <c r="H15" t="n">
-        <v>220</v>
+        <v>218.69999695</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2251,53 +2247,53 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-2.439024390243905</v>
+        <v>-3.015522416851435</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.917076679237251</v>
+        <v>-2.496658949555008</v>
       </c>
       <c r="L15" t="n">
-        <v>1.663588817688955</v>
+        <v>1.062848019793772</v>
       </c>
       <c r="M15" t="n">
-        <v>2030</v>
+        <v>649</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6876847290640394</v>
+        <v>0.662557781201849</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q15" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.680327868852459</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>2027</v>
+        <v>649</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.7636901825357671</v>
+        <v>0.7596302003081664</v>
       </c>
       <c r="W15" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y15" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.7786885245901639</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2334,10 +2330,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>306.75</v>
+        <v>306.5</v>
       </c>
       <c r="H16" t="n">
-        <v>306.75</v>
+        <v>306.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2345,13 +2341,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>-2.153110047846885</v>
+        <v>-2.232854864433809</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.764705882352937</v>
+        <v>-3.843137254901963</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5672609400324102</v>
+        <v>-0.648298217179899</v>
       </c>
       <c r="M16" t="n">
         <v>2030</v>
@@ -2432,24 +2428,24 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>20.4</v>
+        <v>20.42000008</v>
       </c>
       <c r="H17" t="n">
-        <v>20.4</v>
+        <v>20.42000008</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254); H - %68.9 (n=222)</t>
+          <t>B - %75.2 (n=254)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-6.336091121583898</v>
+        <v>-6.244263392628935</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.942237644013339</v>
+        <v>-7.851984574810356</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.133900696152303</v>
+        <v>-3.038933552261858</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
@@ -2530,10 +2526,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>20.52</v>
+        <v>20.52000046</v>
       </c>
       <c r="H18" t="n">
-        <v>20.52</v>
+        <v>20.52000046</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2541,13 +2537,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="L18" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="M18" t="n">
         <v>4284</v>
@@ -2628,10 +2624,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>20.52</v>
+        <v>20.52000046</v>
       </c>
       <c r="H19" t="n">
-        <v>20.52</v>
+        <v>20.52000046</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2639,13 +2635,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="L19" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="M19" t="n">
         <v>6024</v>
@@ -2726,10 +2722,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>150.6</v>
+        <v>150.19999695</v>
       </c>
       <c r="H20" t="n">
-        <v>150.6</v>
+        <v>150.19999695</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2737,13 +2733,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>-3.83142137055128</v>
+        <v>-4.086851149873604</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.761254400705636</v>
+        <v>-2.022182673400785</v>
       </c>
       <c r="L20" t="n">
-        <v>1.619435289738713</v>
+        <v>1.349527693090824</v>
       </c>
       <c r="M20" t="n">
         <v>2030</v>
@@ -2824,10 +2820,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="H21" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2835,13 +2831,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-3.501281286075897</v>
+        <v>-3.928266767110966</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.353608526076272</v>
+        <v>-8.759123532598068</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.583619927503467</v>
+        <v>-4.01024107826673</v>
       </c>
       <c r="M21" t="n">
         <v>2030</v>
@@ -2922,24 +2918,24 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>229.69999695</v>
+        <v>231.5</v>
       </c>
       <c r="H22" t="n">
-        <v>229.69999695</v>
+        <v>231.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>B - %75.2 (n=254); G - %68.8 (n=208)</t>
+          <t>B - %75.2 (n=254)</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.9486834876540229</v>
+        <v>-0.1724855155332494</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5197041930281254</v>
+        <v>0.2598553988095276</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.161788735313729</v>
+        <v>-0.3872607244504778</v>
       </c>
       <c r="M22" t="n">
         <v>930</v>
@@ -3016,10 +3012,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>274.5</v>
+        <v>273.75</v>
       </c>
       <c r="H23" t="n">
-        <v>274.5</v>
+        <v>273.75</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3027,13 +3023,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2.234636871508378</v>
+        <v>1.955307262569828</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2724795640327016</v>
+        <v>-0.544959128065392</v>
       </c>
       <c r="L23" t="n">
-        <v>3.098591549295771</v>
+        <v>2.8169014084507</v>
       </c>
       <c r="M23" t="n">
         <v>2030</v>
@@ -3110,10 +3106,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H24" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3121,13 +3117,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.6156552330694787</v>
+        <v>0.9674582233949014</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.633705932932072</v>
+        <v>-1.289767841788481</v>
       </c>
       <c r="L24" t="n">
-        <v>9.788867562380045</v>
+        <v>10.17274472168905</v>
       </c>
       <c r="M24" t="n">
         <v>2030</v>
@@ -3194,12 +3190,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3208,10 +3204,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>11.25</v>
+        <v>11.22000027</v>
       </c>
       <c r="H25" t="n">
-        <v>11.25</v>
+        <v>11.22000027</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3219,62 +3215,58 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-2.088770886024138</v>
+        <v>-2.349865147125241</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3542954839833246</v>
+        <v>-0.6200149711957925</v>
       </c>
       <c r="L25" t="n">
-        <v>1.902174282254254</v>
+        <v>1.630437596487089</v>
       </c>
       <c r="M25" t="n">
-        <v>2030</v>
+        <v>649</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.6876847290640394</v>
+        <v>0.662557781201849</v>
       </c>
       <c r="O25" t="n">
+        <v>8</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q25" t="n">
         <v>33</v>
       </c>
-      <c r="P25" s="4" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>122</v>
-      </c>
       <c r="R25" s="4" t="n">
-        <v>0.680327868852459</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>649</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0.7596302003081664</v>
+      </c>
+      <c r="W25" t="n">
+        <v>8</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z25" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U25" t="n">
-        <v>2027</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>0.7636901825357671</v>
-      </c>
-      <c r="W25" t="n">
-        <v>33</v>
-      </c>
-      <c r="X25" s="4" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>122</v>
-      </c>
-      <c r="Z25" s="4" t="n">
-        <v>0.7786885245901639</v>
-      </c>
       <c r="AA25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB25" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3306,10 +3298,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>89.45</v>
+        <v>89.59999847</v>
       </c>
       <c r="H26" t="n">
-        <v>89.45</v>
+        <v>89.59999847</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3317,13 +3309,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-4.023602009356075</v>
+        <v>-3.862659439711491</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.042459770483032</v>
+        <v>-4.88322572074138</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9024235264443625</v>
+        <v>1.071626535368431</v>
       </c>
       <c r="M26" t="n">
         <v>2030</v>
@@ -3400,10 +3392,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2.46</v>
+        <v>2.45000005</v>
       </c>
       <c r="H27" t="n">
-        <v>2.46</v>
+        <v>2.45000005</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3411,13 +3403,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2.074684984762798</v>
+        <v>1.659749315611014</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.380951606198034</v>
+        <v>-2.777775022045847</v>
       </c>
       <c r="L27" t="n">
-        <v>6.956524064272251</v>
+        <v>6.521743620037901</v>
       </c>
       <c r="M27" t="n">
         <v>5102</v>
@@ -9248,7 +9240,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>33.95999908</v>
+        <v>34.88000107</v>
       </c>
       <c r="H2" t="n">
         <v>2027</v>
@@ -9349,7 +9341,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11.09</v>
+        <v>11.11999989</v>
       </c>
       <c r="H3" t="n">
         <v>2027</v>
@@ -9454,7 +9446,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>109.1</v>
+        <v>109.5</v>
       </c>
       <c r="H4" t="n">
         <v>2027</v>
@@ -9557,7 +9549,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>89.8</v>
+        <v>89.75</v>
       </c>
       <c r="H5" t="n">
         <v>649</v>
@@ -9656,7 +9648,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>380</v>
+        <v>379.75</v>
       </c>
       <c r="H6" t="n">
         <v>2027</v>
@@ -9761,7 +9753,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H7" t="n">
         <v>2027</v>
@@ -9847,17 +9839,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Morning Star</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9866,80 +9858,74 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>80.45</v>
+        <v>666</v>
       </c>
       <c r="H8" t="n">
-        <v>2027</v>
+        <v>928</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.5742476566354218</v>
+        <v>0.572198275862069</v>
       </c>
       <c r="J8" t="n">
-        <v>1393</v>
+        <v>608</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.7709978463747308</v>
+        <v>0.7664473684210527</v>
       </c>
       <c r="L8" t="n">
-        <v>1548</v>
+        <v>703</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.751937984496124</v>
+        <v>0.7553342816500711</v>
       </c>
       <c r="N8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.6</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.75</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
       <c r="T8" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.5327868852459017</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="V8" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="X8" t="n">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9952,17 +9938,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Piercing Line</t>
+          <t>Bullish Engulfing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9971,74 +9957,80 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20.94</v>
+        <v>80.40000153</v>
       </c>
       <c r="H9" t="n">
-        <v>649</v>
+        <v>2027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.5701078582434514</v>
+        <v>0.5742476566354218</v>
       </c>
       <c r="J9" t="n">
-        <v>430</v>
+        <v>1393</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.7813953488372093</v>
+        <v>0.7709978463747308</v>
       </c>
       <c r="L9" t="n">
-        <v>493</v>
+        <v>1548</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7505070993914807</v>
+        <v>0.751937984496124</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="T9" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.5327868852459017</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7590361445783133</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC9" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE9" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10070,7 +10062,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>63.95</v>
+        <v>64.30000305</v>
       </c>
       <c r="H10" t="n">
         <v>649</v>
@@ -10169,7 +10161,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>132.9</v>
+        <v>132.5</v>
       </c>
       <c r="H11" t="n">
         <v>2027</v>
@@ -10270,7 +10262,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.97</v>
+        <v>0.97000003</v>
       </c>
       <c r="H12" t="n">
         <v>2413</v>
@@ -10355,12 +10347,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10369,80 +10361,74 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13.44</v>
+        <v>13.36999989</v>
       </c>
       <c r="H13" t="n">
-        <v>2027</v>
+        <v>649</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5742476566354218</v>
+        <v>0.5701078582434514</v>
       </c>
       <c r="J13" t="n">
-        <v>1393</v>
+        <v>430</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7709978463747308</v>
+        <v>0.7813953488372093</v>
       </c>
       <c r="L13" t="n">
-        <v>1548</v>
+        <v>493</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.751937984496124</v>
+        <v>0.7505070993914807</v>
       </c>
       <c r="N13" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6</v>
       </c>
       <c r="R13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.6</v>
       </c>
       <c r="T13" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.5327868852459017</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="V13" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="X13" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA13" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10474,7 +10460,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35.02</v>
+        <v>34.72000122</v>
       </c>
       <c r="H14" t="n">
         <v>2027</v>
@@ -10565,12 +10551,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10579,61 +10565,61 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>220</v>
+        <v>218.69999695</v>
       </c>
       <c r="H15" t="n">
-        <v>2027</v>
+        <v>649</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5742476566354218</v>
+        <v>0.5701078582434514</v>
       </c>
       <c r="J15" t="n">
-        <v>1393</v>
+        <v>430</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7709978463747308</v>
+        <v>0.7813953488372093</v>
       </c>
       <c r="L15" t="n">
-        <v>1548</v>
+        <v>493</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.751937984496124</v>
+        <v>0.7505070993914807</v>
       </c>
       <c r="N15" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O15" s="4" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>0.75</v>
-      </c>
       <c r="R15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="T15" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.5327868852459017</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="V15" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="X15" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -10678,7 +10664,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>306.75</v>
+        <v>306.5</v>
       </c>
       <c r="H16" t="n">
         <v>2027</v>
@@ -10783,7 +10769,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>20.4</v>
+        <v>20.42000008</v>
       </c>
       <c r="H17" t="n">
         <v>649</v>
@@ -10884,7 +10870,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>20.52</v>
+        <v>20.52000046</v>
       </c>
       <c r="H18" t="n">
         <v>4283</v>
@@ -10989,7 +10975,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>20.52</v>
+        <v>20.52000046</v>
       </c>
       <c r="H19" t="n">
         <v>6022</v>
@@ -11094,7 +11080,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>150.6</v>
+        <v>150.19999695</v>
       </c>
       <c r="H20" t="n">
         <v>2027</v>
@@ -11195,7 +11181,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="H21" t="n">
         <v>2027</v>
@@ -11300,7 +11286,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>229.69999695</v>
+        <v>231.5</v>
       </c>
       <c r="H22" t="n">
         <v>928</v>
@@ -11399,7 +11385,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>274.5</v>
+        <v>273.75</v>
       </c>
       <c r="H23" t="n">
         <v>2027</v>
@@ -11498,7 +11484,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H24" t="n">
         <v>2027</v>
@@ -11589,12 +11575,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11603,80 +11589,74 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>11.25</v>
+        <v>11.22000027</v>
       </c>
       <c r="H25" t="n">
-        <v>2027</v>
+        <v>649</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.5742476566354218</v>
+        <v>0.5701078582434514</v>
       </c>
       <c r="J25" t="n">
-        <v>1393</v>
+        <v>430</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.7709978463747308</v>
+        <v>0.7813953488372093</v>
       </c>
       <c r="L25" t="n">
-        <v>1548</v>
+        <v>493</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.751937984496124</v>
+        <v>0.7505070993914807</v>
       </c>
       <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>33</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>0.4848484848484849</v>
       </c>
-      <c r="P25" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="R25" t="n">
-        <v>20</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>122</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>0.5327868852459017</v>
-      </c>
       <c r="V25" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="X25" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA25" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC25" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="4" t="inlineStr"/>
       <c r="AD25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE25" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11708,7 +11688,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>89.45</v>
+        <v>89.59999847</v>
       </c>
       <c r="H26" t="n">
         <v>2027</v>
@@ -11807,7 +11787,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2.46</v>
+        <v>2.45000005</v>
       </c>
       <c r="H27" t="n">
         <v>5101</v>
@@ -12938,7 +12918,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="47" customWidth="1" min="11" max="11"/>
@@ -13116,57 +13096,61 @@
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.508122003878654</v>
+        <v>1.160097260256521</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>469</v>
+        <v>650</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.6375266524520256</v>
+        <v>0.6430769230769231</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
-        <v>467</v>
+        <v>650</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.7109207708779444</v>
+        <v>0.7492307692307693</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.875</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="V2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>0.696969696969697</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13199,57 +13183,61 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.508122003878654</v>
+        <v>1.160097260256521</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>636</v>
+        <v>1018</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.6797642436149313</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.625</v>
       </c>
       <c r="N3" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
-        <v>634</v>
+        <v>1018</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.769155206286837</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.75</v>
       </c>
       <c r="V3" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.8245614035087719</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13282,57 +13270,61 @@
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.508122003878654</v>
+        <v>1.160097260256521</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>699</v>
+        <v>1175</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.6566523605150214</v>
+        <v>0.6927659574468085</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.625</v>
       </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.7538461538461538</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
-        <v>697</v>
+        <v>1174</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.7302725968436155</v>
+        <v>0.7768313458262351</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.75</v>
       </c>
       <c r="V4" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13365,52 +13357,52 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1176497647058738</v>
+        <v>2.58823844117646</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[2,4)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>501</v>
+        <v>193</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.6686626746506986</v>
+        <v>0.7202072538860104</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>501</v>
+        <v>193</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.7405189620758483</v>
+        <v>0.7823834196891192</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -13448,57 +13440,61 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1176497647058738</v>
+        <v>2.58823844117646</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>884</v>
+        <v>555</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6481900452488688</v>
+        <v>0.6882882882882883</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="N6" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.640625</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
-        <v>884</v>
+        <v>555</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.7262443438914027</v>
+        <v>0.7765765765765765</v>
       </c>
       <c r="T6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="V6" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.765625</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13531,57 +13527,61 @@
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1176497647058738</v>
+        <v>2.58823844117646</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1095</v>
+        <v>648</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.6602739726027397</v>
+        <v>0.7052469135802469</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N7" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.625</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R7" t="n">
-        <v>1094</v>
+        <v>648</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.7394881170018281</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="T7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="V7" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13614,52 +13614,48 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.971496524162776</v>
+        <v>5.761072033053138</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[4,6)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.6462585034013606</v>
+        <v>0.7375</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.7551020408163265</v>
+        <v>0.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -13697,61 +13693,57 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.971496524162776</v>
+        <v>5.761072033053138</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>384</v>
+        <v>119</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.6901041666666666</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>384</v>
+        <v>119</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.7786458333333334</v>
+        <v>0.8403361344537815</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13784,7 +13776,7 @@
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.971496524162776</v>
+        <v>5.761072033053138</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -13871,57 +13863,61 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.352569867218989e-06</v>
+        <v>0.2705116284421383</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>469</v>
+        <v>650</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.6375266524520256</v>
+        <v>0.6430769230769231</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R11" t="n">
-        <v>467</v>
+        <v>650</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7109207708779444</v>
+        <v>0.7492307692307693</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.696969696969697</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13954,57 +13950,61 @@
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.352569867218989e-06</v>
+        <v>0.2705116284421383</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>636</v>
+        <v>1018</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.6797642436149313</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="n">
-        <v>634</v>
+        <v>1018</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.769155206286837</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.8245614035087719</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14037,57 +14037,61 @@
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.352569867218989e-06</v>
+        <v>0.2705116284421383</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>699</v>
+        <v>1175</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6566523605150214</v>
+        <v>0.6927659574468085</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N13" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.7538461538461538</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="n">
-        <v>697</v>
+        <v>1174</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.7302725968436155</v>
+        <v>0.7768313458262351</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14120,57 +14124,61 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.204586831508992</v>
+        <v>-1.940037540475681</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>383</v>
+        <v>501</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6214099216710183</v>
+        <v>0.6686626746506986</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M14" s="4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="N14" t="n">
+        <v>36</v>
+      </c>
+      <c r="O14" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="N14" t="n">
-        <v>28</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>0.6071428571428571</v>
-      </c>
       <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="n">
-        <v>383</v>
+        <v>501</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.7075718015665796</v>
+        <v>0.7405189620758483</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.75</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14203,7 +14211,7 @@
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.204586831508992</v>
+        <v>-1.940037540475681</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -14290,7 +14298,7 @@
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.204586831508992</v>
+        <v>-1.940037540475681</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -14377,7 +14385,7 @@
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.229319977634516</v>
+        <v>4.511273822008177</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -14456,7 +14464,7 @@
         <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.229319977634516</v>
+        <v>4.511273822008177</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -14539,7 +14547,7 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.229319977634516</v>
+        <v>4.511273822008177</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -14622,7 +14630,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.621905530448877</v>
+        <v>-3.268548630468848</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -14701,7 +14709,7 @@
         <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.621905530448877</v>
+        <v>-3.268548630468848</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -14788,7 +14796,7 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.621905530448877</v>
+        <v>-3.268548630468848</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -14875,7 +14883,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.432245770508893</v>
+        <v>-6.089192592765569</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -14958,7 +14966,7 @@
         <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.432245770508893</v>
+        <v>-6.089192592765569</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -15041,7 +15049,7 @@
         <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.432245770508893</v>
+        <v>-6.089192592765569</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -15124,61 +15132,57 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.327660717093694</v>
+        <v>-1.969558648228775</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5807560137457045</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.7356687898089171</v>
+        <v>0.7010309278350515</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15211,7 +15215,7 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.327660717093694</v>
+        <v>-1.969558648228775</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -15298,7 +15302,7 @@
         <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.327660717093694</v>
+        <v>-1.969558648228775</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -15385,7 +15389,7 @@
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.822467984932444</v>
+        <v>-4.875462156433041</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -15468,7 +15472,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.822467984932444</v>
+        <v>-4.875462156433041</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -15551,7 +15555,7 @@
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>-4.822467984932444</v>
+        <v>-4.875462156433041</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -15634,7 +15638,7 @@
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.374079502398931</v>
+        <v>-5.426766540537898</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -15717,7 +15721,7 @@
         <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>-5.374079502398931</v>
+        <v>-5.426766540537898</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -15800,7 +15804,7 @@
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>-5.374079502398931</v>
+        <v>-5.426766540537898</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -15883,7 +15887,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.069219523195342</v>
+        <v>1.012944902079971</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -15966,7 +15970,7 @@
         <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>1.069219523195342</v>
+        <v>1.012944902079971</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -16049,7 +16053,7 @@
         <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>1.069219523195342</v>
+        <v>1.012944902079971</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -16132,61 +16136,57 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.013422818791955</v>
+        <v>1.946308724832213</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>368</v>
+        <v>650</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.7445652173913043</v>
+        <v>0.6430769230769231</v>
       </c>
       <c r="L38" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N38" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>368</v>
+        <v>650</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.7492307692307693</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V38" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="W38" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16219,7 +16219,7 @@
         <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>2.013422818791955</v>
+        <v>1.946308724832213</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>2.013422818791955</v>
+        <v>1.946308724832213</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.642409033877037</v>
+        <v>-4.70514429109159</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>-4.642409033877037</v>
+        <v>-4.70514429109159</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.642409033877037</v>
+        <v>-4.70514429109159</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.06574621959237748</v>
+        <v>-0.1314924391847438</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.06574621959237748</v>
+        <v>-0.1314924391847438</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.06574621959237748</v>
+        <v>-0.1314924391847438</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>-3.003663003663004</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>-3.003663003663004</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.003663003663004</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -17140,52 +17140,52 @@
         <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>-6.03264726756565</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[-8,-6)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7109004739336493</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="4" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.7952380952380952</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W50" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -17223,7 +17223,7 @@
         <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>-6.03264726756565</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -17306,57 +17306,61 @@
         <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>-6.03264726756565</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[-12,-6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>170</v>
+        <v>1095</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.6602739726027397</v>
       </c>
       <c r="L52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N52" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.625</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="n">
-        <v>169</v>
+        <v>1094</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>0.8224852071005917</v>
+        <v>0.7394881170018281</v>
       </c>
       <c r="T52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="V52" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="W52" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y52" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17389,7 +17393,7 @@
         <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>-3.779069767441856</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -17476,7 +17480,7 @@
         <v>4</v>
       </c>
       <c r="H54" t="n">
-        <v>-3.779069767441856</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -17563,7 +17567,7 @@
         <v>6</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.779069767441856</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -17630,12 +17634,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -17650,52 +17654,52 @@
         <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2479870132743867</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>469</v>
+        <v>48</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.6375266524520256</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="L56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.5151515151515151</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="4" t="inlineStr"/>
       <c r="R56" t="n">
-        <v>467</v>
+        <v>48</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>0.7109207708779444</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>0.696969696969697</v>
+        <v>1</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -17713,12 +17717,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -17733,7 +17737,7 @@
         <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2479870132743867</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -17741,44 +17745,44 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>636</v>
+        <v>247</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.5951417004048583</v>
       </c>
       <c r="L57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>634</v>
+        <v>247</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.708502024291498</v>
       </c>
       <c r="T57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -17796,12 +17800,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -17816,7 +17820,7 @@
         <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2479870132743867</v>
+        <v>-2.41758241758242</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -17824,44 +17828,44 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>699</v>
+        <v>253</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.6566523605150214</v>
+        <v>0.6007905138339921</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="4" t="inlineStr"/>
       <c r="R58" t="n">
-        <v>697</v>
+        <v>253</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>0.7302725968436155</v>
+        <v>0.7154150197628458</v>
       </c>
       <c r="T58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="V58" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="W58" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
@@ -17879,12 +17883,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -17899,48 +17903,48 @@
         <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>1.19496855345913</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>362</v>
+        <v>68</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0.6712707182320442</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="4" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="4" t="inlineStr"/>
       <c r="R59" t="n">
-        <v>362</v>
+        <v>68</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>0.7734806629834254</v>
+        <v>0.75</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
       <c r="U59" s="4" t="inlineStr"/>
       <c r="V59" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="W59" s="4" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -17958,12 +17962,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -17978,52 +17982,52 @@
         <v>4</v>
       </c>
       <c r="H60" t="n">
-        <v>1.19496855345913</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>555</v>
+        <v>111</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.6882882882882883</v>
+        <v>0.6576576576576577</v>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.75</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="4" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>555</v>
+        <v>111</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.7765765765765765</v>
+        <v>0.7117117117117117</v>
       </c>
       <c r="T60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.75</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -18041,12 +18045,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -18061,52 +18065,52 @@
         <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>1.19496855345913</v>
+        <v>-5.464868701206527</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>648</v>
+        <v>452</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0.7052469135802469</v>
+        <v>0.6106194690265486</v>
       </c>
       <c r="L61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N61" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.75</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="4" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>648</v>
+        <v>451</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>0.7901234567901234</v>
+        <v>0.7184035476718403</v>
       </c>
       <c r="T61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="V61" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -18124,12 +18128,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -18144,48 +18148,48 @@
         <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>2.093904677837455</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.6462585034013606</v>
+        <v>0.5949367088607594</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="4" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>0.7551020408163265</v>
+        <v>0.6962025316455697</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" s="4" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -18203,12 +18207,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -18223,61 +18227,57 @@
         <v>4</v>
       </c>
       <c r="H63" t="n">
-        <v>2.093904677837455</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0.6901041666666666</v>
+        <v>0.5798611111111112</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>0.7786458333333334</v>
+        <v>0.7048611111111112</v>
       </c>
       <c r="T63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U63" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="V63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="X63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y63" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -18310,61 +18310,57 @@
         <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>2.093904677837455</v>
+        <v>-3.197674418604646</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0.6982758620689655</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="L64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N64" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="4" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>0.7823275862068966</v>
+        <v>0.7306791569086651</v>
       </c>
       <c r="T64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U64" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="V64" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="W64" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="X64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y64" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18377,12 +18373,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -18397,52 +18393,52 @@
         <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>-3.679851786861355</v>
+        <v>-0.3099813952353148</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>167</v>
+        <v>469</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0.688622754491018</v>
+        <v>0.6375266524520256</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="4" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>0.8143712574850299</v>
+        <v>0.7109207708779444</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V65" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="W65" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -18460,12 +18456,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -18480,7 +18476,7 @@
         <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.679851786861355</v>
+        <v>-0.3099813952353148</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -18488,44 +18484,44 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>378</v>
+        <v>636</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0.6693121693121693</v>
+        <v>0.64937106918239</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="N66" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="4" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>378</v>
+        <v>634</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>0.7751322751322751</v>
+        <v>0.7208201892744479</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="V66" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -18543,12 +18539,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -18563,7 +18559,7 @@
         <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>-3.679851786861355</v>
+        <v>-0.3099813952353148</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -18571,44 +18567,44 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>447</v>
+        <v>699</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.6756152125279642</v>
+        <v>0.6566523605150214</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="N67" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="4" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>447</v>
+        <v>697</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>0.7740492170022372</v>
+        <v>0.7302725968436155</v>
       </c>
       <c r="T67" t="n">
         <v>5</v>
       </c>
       <c r="U67" s="4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="V67" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
@@ -18626,12 +18622,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -18646,52 +18642,48 @@
         <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>-3.234747734436039</v>
+        <v>1.132077396226405</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>151</v>
+        <v>362</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0.6622516556291391</v>
+        <v>0.6712707182320442</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M68" s="4" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="4" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>151</v>
+        <v>362</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>0.7880794701986755</v>
+        <v>0.7734806629834254</v>
       </c>
       <c r="T68" t="n">
-        <v>2</v>
-      </c>
-      <c r="U68" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U68" s="4" t="inlineStr"/>
       <c r="V68" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W68" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
@@ -18709,12 +18701,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -18729,52 +18721,52 @@
         <v>4</v>
       </c>
       <c r="H69" t="n">
-        <v>-3.234747734436039</v>
+        <v>1.132077396226405</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>274</v>
+        <v>555</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0.6386861313868614</v>
+        <v>0.6882882882882883</v>
       </c>
       <c r="L69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="N69" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="4" t="inlineStr"/>
       <c r="R69" t="n">
-        <v>274</v>
+        <v>555</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>0.7481751824817519</v>
+        <v>0.7765765765765765</v>
       </c>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V69" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="W69" s="4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
@@ -18792,12 +18784,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -18812,52 +18804,52 @@
         <v>6</v>
       </c>
       <c r="H70" t="n">
-        <v>-3.234747734436039</v>
+        <v>1.132077396226405</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>399</v>
+        <v>648</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.6365914786967418</v>
+        <v>0.7052469135802469</v>
       </c>
       <c r="L70" t="n">
         <v>6</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="N70" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="4" t="inlineStr"/>
       <c r="R70" t="n">
-        <v>399</v>
+        <v>648</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>0.7443609022556391</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="T70" t="n">
         <v>6</v>
       </c>
       <c r="U70" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V70" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="X70" t="n">
         <v>0</v>
@@ -18875,12 +18867,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -18895,52 +18887,48 @@
         <v>2</v>
       </c>
       <c r="H71" t="n">
-        <v>-2.240896723656782</v>
+        <v>2.030454845267915</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[2,4)</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0.594059405940594</v>
+        <v>0.6462585034013606</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M71" s="4" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="4" t="inlineStr"/>
       <c r="R71" t="n">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>0.7425742574257426</v>
+        <v>0.7551020408163265</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U71" s="4" t="inlineStr"/>
       <c r="V71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W71" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -18958,12 +18946,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -18978,57 +18966,61 @@
         <v>4</v>
       </c>
       <c r="H72" t="n">
-        <v>-2.240896723656782</v>
+        <v>2.030454845267915</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>167</v>
+        <v>384</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.6107784431137725</v>
+        <v>0.6901041666666666</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N72" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O72" s="4" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>384</v>
+      </c>
+      <c r="S72" s="4" t="n">
+        <v>0.7786458333333334</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="4" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>167</v>
-      </c>
-      <c r="S72" s="4" t="n">
-        <v>0.7485029940119761</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1</v>
-      </c>
-      <c r="U72" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="V72" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W72" s="4" t="n">
-        <v>0.6</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y72" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -19041,12 +19033,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PIERCING_LINE</t>
+          <t>BULLISH_ENGULFING</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -19061,57 +19053,61 @@
         <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>-2.240896723656782</v>
+        <v>2.030454845267915</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>259</v>
+        <v>464</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0.61003861003861</v>
+        <v>0.6982758620689655</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N73" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R73" t="n">
-        <v>259</v>
+        <v>464</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>0.7335907335907336</v>
+        <v>0.7823275862068966</v>
       </c>
       <c r="T73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U73" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V73" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W73" s="4" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y73" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -19144,7 +19140,7 @@
         <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>-7.919362406825847</v>
+        <v>-7.41539830981951</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -19219,7 +19215,7 @@
         <v>4</v>
       </c>
       <c r="H75" t="n">
-        <v>-7.919362406825847</v>
+        <v>-7.41539830981951</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -19302,7 +19298,7 @@
         <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>-7.919362406825847</v>
+        <v>-7.41539830981951</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -19381,7 +19377,7 @@
         <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>-10.68435563333888</v>
+        <v>-10.1955245474742</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -19460,7 +19456,7 @@
         <v>4</v>
       </c>
       <c r="H78" t="n">
-        <v>-10.68435563333888</v>
+        <v>-10.1955245474742</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -19539,7 +19535,7 @@
         <v>6</v>
       </c>
       <c r="H79" t="n">
-        <v>-10.68435563333888</v>
+        <v>-10.1955245474742</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -19618,7 +19614,7 @@
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>-8.642857142857141</v>
+        <v>-8.142852785714283</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -19701,7 +19697,7 @@
         <v>4</v>
       </c>
       <c r="H81" t="n">
-        <v>-8.642857142857141</v>
+        <v>-8.142852785714283</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -19784,7 +19780,7 @@
         <v>6</v>
       </c>
       <c r="H82" t="n">
-        <v>-8.642857142857141</v>
+        <v>-8.142852785714283</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -19867,7 +19863,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.7468214679283824</v>
+        <v>-1.045551877355233</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -19954,7 +19950,7 @@
         <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.7468214679283824</v>
+        <v>-1.045551877355233</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -20041,7 +20037,7 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.7468214679283824</v>
+        <v>-1.045551877355233</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -20128,7 +20124,7 @@
         <v>2</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.3748080381283936</v>
+        <v>-0.6746581268022078</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -20211,7 +20207,7 @@
         <v>4</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.3748080381283936</v>
+        <v>-0.6746581268022078</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -20294,7 +20290,7 @@
         <v>6</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.3748080381283936</v>
+        <v>-0.6746581268022078</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -20381,7 +20377,7 @@
         <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>1.141557206723731</v>
+        <v>0.837143189547751</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -20464,7 +20460,7 @@
         <v>4</v>
       </c>
       <c r="H90" t="n">
-        <v>1.141557206723731</v>
+        <v>0.837143189547751</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -20547,7 +20543,7 @@
         <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>1.141557206723731</v>
+        <v>0.837143189547751</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -20630,7 +20626,7 @@
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -20713,7 +20709,7 @@
         <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -20796,7 +20792,7 @@
         <v>6</v>
       </c>
       <c r="H94" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -20879,7 +20875,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>-4.901958919646243</v>
+        <v>-4.901955978469719</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -20962,7 +20958,7 @@
         <v>4</v>
       </c>
       <c r="H96" t="n">
-        <v>-4.901958919646243</v>
+        <v>-4.901955978469719</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -21045,7 +21041,7 @@
         <v>6</v>
       </c>
       <c r="H97" t="n">
-        <v>-4.901958919646243</v>
+        <v>-4.901955978469719</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -21128,7 +21124,7 @@
         <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -21211,7 +21207,7 @@
         <v>4</v>
       </c>
       <c r="H99" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -21294,7 +21290,7 @@
         <v>6</v>
       </c>
       <c r="H100" t="n">
-        <v>-3.960395088716795</v>
+        <v>-3.960392118419731</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -21362,7 +21358,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -21377,7 +21373,7 @@
         <v>2</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.890174462895512</v>
+        <v>-3.395955599032263</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -21388,19 +21384,19 @@
         <v>167</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0.6826347305389222</v>
+        <v>0.688622754491018</v>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M101" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>0.4</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -21410,19 +21406,19 @@
         <v>167</v>
       </c>
       <c r="S101" s="4" t="n">
-        <v>0.7485029940119761</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="T101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U101" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="V101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W101" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -21445,7 +21441,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -21460,7 +21456,7 @@
         <v>4</v>
       </c>
       <c r="H102" t="n">
-        <v>-2.890174462895512</v>
+        <v>-3.395955599032263</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -21468,44 +21464,44 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>636</v>
+        <v>378</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.6693121693121693</v>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N102" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="4" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>634</v>
+        <v>378</v>
       </c>
       <c r="S102" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.7751322751322751</v>
       </c>
       <c r="T102" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U102" s="4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="V102" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="W102" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -21528,7 +21524,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -21543,7 +21539,7 @@
         <v>6</v>
       </c>
       <c r="H103" t="n">
-        <v>-2.890174462895512</v>
+        <v>-3.395955599032263</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -21551,44 +21547,44 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>699</v>
+        <v>447</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0.6566523605150214</v>
+        <v>0.6756152125279642</v>
       </c>
       <c r="L103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M103" s="4" t="n">
-        <v>0.6</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N103" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="4" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>697</v>
+        <v>447</v>
       </c>
       <c r="S103" s="4" t="n">
-        <v>0.7302725968436155</v>
+        <v>0.7740492170022372</v>
       </c>
       <c r="T103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U103" s="4" t="n">
-        <v>0.7</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="V103" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="W103" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
@@ -21611,7 +21607,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -21626,7 +21622,7 @@
         <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.183404476141426</v>
+        <v>-2.692866711743769</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -21634,53 +21630,49 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>383</v>
+        <v>151</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0.6214099216710183</v>
+        <v>0.6622516556291391</v>
       </c>
       <c r="L104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M104" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N104" t="n">
+        <v>12</v>
+      </c>
+      <c r="O104" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="N104" t="n">
-        <v>28</v>
-      </c>
-      <c r="O104" s="4" t="n">
-        <v>0.6071428571428571</v>
-      </c>
       <c r="P104" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q104" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q104" s="4" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>383</v>
+        <v>151</v>
       </c>
       <c r="S104" s="4" t="n">
-        <v>0.7075718015665796</v>
+        <v>0.7880794701986755</v>
       </c>
       <c r="T104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U104" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="V104" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="W104" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="X104" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y104" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -21698,7 +21690,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -21713,7 +21705,7 @@
         <v>4</v>
       </c>
       <c r="H105" t="n">
-        <v>-2.183404476141426</v>
+        <v>-2.692866711743769</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -21721,53 +21713,49 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>884</v>
+        <v>274</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0.6481900452488688</v>
+        <v>0.6386861313868614</v>
       </c>
       <c r="L105" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M105" s="4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5</v>
       </c>
       <c r="N105" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>0.640625</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q105" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q105" s="4" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>884</v>
+        <v>274</v>
       </c>
       <c r="S105" s="4" t="n">
-        <v>0.7262443438914027</v>
+        <v>0.7481751824817519</v>
       </c>
       <c r="T105" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="U105" s="4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5</v>
       </c>
       <c r="V105" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="W105" s="4" t="n">
-        <v>0.765625</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="X105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y105" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -21785,7 +21773,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -21800,7 +21788,7 @@
         <v>6</v>
       </c>
       <c r="H106" t="n">
-        <v>-2.183404476141426</v>
+        <v>-2.692866711743769</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -21808,53 +21796,49 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>1095</v>
+        <v>399</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.6602739726027397</v>
+        <v>0.6365914786967418</v>
       </c>
       <c r="L106" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N106" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.625</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q106" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q106" s="4" t="inlineStr"/>
       <c r="R106" t="n">
-        <v>1094</v>
+        <v>399</v>
       </c>
       <c r="S106" s="4" t="n">
-        <v>0.7394881170018281</v>
+        <v>0.7443609022556391</v>
       </c>
       <c r="T106" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U106" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V106" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="W106" s="4" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="X106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y106" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -21872,7 +21856,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -21887,7 +21871,7 @@
         <v>2</v>
       </c>
       <c r="H107" t="n">
-        <v>3.783785306480247</v>
+        <v>3.243243908588145</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -21895,53 +21879,41 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0.6462585034013606</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L107" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M107" s="4" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>4</v>
-      </c>
-      <c r="O107" s="4" t="n">
-        <v>0.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O107" s="4" t="inlineStr"/>
       <c r="P107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q107" s="4" t="inlineStr"/>
       <c r="R107" t="n">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="S107" s="4" t="n">
-        <v>0.7551020408163265</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="T107" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U107" s="4" t="inlineStr"/>
       <c r="V107" t="n">
-        <v>4</v>
-      </c>
-      <c r="W107" s="4" t="n">
-        <v>0.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W107" s="4" t="inlineStr"/>
       <c r="X107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y107" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -21959,7 +21931,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -21974,7 +21946,7 @@
         <v>4</v>
       </c>
       <c r="H108" t="n">
-        <v>3.783785306480247</v>
+        <v>3.243243908588145</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -21982,53 +21954,49 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.6901041666666666</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="L108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q108" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q108" s="4" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="S108" s="4" t="n">
-        <v>0.7786458333333334</v>
+        <v>0.7288135593220338</v>
       </c>
       <c r="T108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U108" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W108" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="X108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y108" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22046,7 +22014,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -22061,7 +22029,7 @@
         <v>6</v>
       </c>
       <c r="H109" t="n">
-        <v>3.783785306480247</v>
+        <v>3.243243908588145</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -22069,53 +22037,49 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0.6982758620689655</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
         <v>4</v>
       </c>
-      <c r="M109" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N109" t="n">
-        <v>15</v>
-      </c>
       <c r="O109" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="P109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q109" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q109" s="4" t="inlineStr"/>
       <c r="R109" t="n">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="S109" s="4" t="n">
-        <v>0.7823275862068966</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="T109" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
         <v>4</v>
       </c>
-      <c r="U109" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V109" t="n">
-        <v>15</v>
-      </c>
       <c r="W109" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="X109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y109" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -22148,61 +22112,57 @@
         <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1716273500542709</v>
+        <v>-0.6864927526193831</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>650</v>
+        <v>469</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.6430769230769231</v>
+        <v>0.6375266524520256</v>
       </c>
       <c r="L110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N110" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q110" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="4" t="inlineStr"/>
       <c r="R110" t="n">
-        <v>650</v>
+        <v>467</v>
       </c>
       <c r="S110" s="4" t="n">
-        <v>0.7492307692307693</v>
+        <v>0.7109207708779444</v>
       </c>
       <c r="T110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U110" s="4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V110" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="W110" s="4" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="X110" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y110" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -22235,61 +22195,57 @@
         <v>4</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1716273500542709</v>
+        <v>-0.6864927526193831</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>1018</v>
+        <v>636</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0.6797642436149313</v>
+        <v>0.64937106918239</v>
       </c>
       <c r="L111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M111" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.625</v>
       </c>
       <c r="N111" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O111" s="4" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="P111" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q111" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q111" s="4" t="inlineStr"/>
       <c r="R111" t="n">
-        <v>1018</v>
+        <v>634</v>
       </c>
       <c r="S111" s="4" t="n">
-        <v>0.769155206286837</v>
+        <v>0.7208201892744479</v>
       </c>
       <c r="T111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U111" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.625</v>
       </c>
       <c r="V111" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="W111" s="4" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="X111" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y111" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -22322,61 +22278,57 @@
         <v>6</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1716273500542709</v>
+        <v>-0.6864927526193831</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>1175</v>
+        <v>699</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.6927659574468085</v>
+        <v>0.6566523605150214</v>
       </c>
       <c r="L112" t="n">
         <v>10</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="N112" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.7538461538461538</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="P112" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q112" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q112" s="4" t="inlineStr"/>
       <c r="R112" t="n">
-        <v>1174</v>
+        <v>697</v>
       </c>
       <c r="S112" s="4" t="n">
-        <v>0.7768313458262351</v>
+        <v>0.7302725968436155</v>
       </c>
       <c r="T112" t="n">
         <v>10</v>
       </c>
       <c r="U112" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="V112" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="W112" s="4" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="X112" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y112" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -22409,7 +22361,7 @@
         <v>2</v>
       </c>
       <c r="H113" t="n">
-        <v>-2.396881394518857</v>
+        <v>-3.232998370699325</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -22496,7 +22448,7 @@
         <v>4</v>
       </c>
       <c r="H114" t="n">
-        <v>-2.396881394518857</v>
+        <v>-3.232998370699325</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -22583,7 +22535,7 @@
         <v>6</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.396881394518857</v>
+        <v>-3.232998370699325</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -22670,7 +22622,7 @@
         <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>-1.129300368905117</v>
+        <v>-1.976276076131711</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -22753,7 +22705,7 @@
         <v>4</v>
       </c>
       <c r="H117" t="n">
-        <v>-1.129300368905117</v>
+        <v>-1.976276076131711</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -22840,7 +22792,7 @@
         <v>6</v>
       </c>
       <c r="H118" t="n">
-        <v>-1.129300368905117</v>
+        <v>-1.976276076131711</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -22912,7 +22864,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -22927,7 +22879,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="n">
-        <v>-2.439024390243905</v>
+        <v>-3.015522416851435</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -22938,7 +22890,7 @@
         <v>167</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0.6826347305389222</v>
+        <v>0.688622754491018</v>
       </c>
       <c r="L119" t="n">
         <v>2</v>
@@ -22947,10 +22899,10 @@
         <v>0.5</v>
       </c>
       <c r="N119" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>0.4</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -22960,19 +22912,19 @@
         <v>167</v>
       </c>
       <c r="S119" s="4" t="n">
-        <v>0.7485029940119761</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="T119" t="n">
         <v>2</v>
       </c>
       <c r="U119" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V119" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W119" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -22995,7 +22947,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -23010,7 +22962,7 @@
         <v>4</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.439024390243905</v>
+        <v>-3.015522416851435</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -23018,44 +22970,44 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>636</v>
+        <v>378</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.6693121693121693</v>
       </c>
       <c r="L120" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="N120" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="4" t="inlineStr"/>
       <c r="R120" t="n">
-        <v>634</v>
+        <v>378</v>
       </c>
       <c r="S120" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.7751322751322751</v>
       </c>
       <c r="T120" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U120" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="V120" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="W120" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -23078,7 +23030,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -23093,7 +23045,7 @@
         <v>6</v>
       </c>
       <c r="H121" t="n">
-        <v>-2.439024390243905</v>
+        <v>-3.015522416851435</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -23101,44 +23053,44 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>699</v>
+        <v>447</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0.6566523605150214</v>
+        <v>0.6756152125279642</v>
       </c>
       <c r="L121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="N121" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="4" t="inlineStr"/>
       <c r="R121" t="n">
-        <v>697</v>
+        <v>447</v>
       </c>
       <c r="S121" s="4" t="n">
-        <v>0.7302725968436155</v>
+        <v>0.7740492170022372</v>
       </c>
       <c r="T121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U121" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="V121" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="W121" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -23161,7 +23113,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -23176,52 +23128,52 @@
         <v>2</v>
       </c>
       <c r="H122" t="n">
-        <v>-1.917076679237251</v>
+        <v>-2.496658949555008</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.6686626746506986</v>
+        <v>0.6622516556291391</v>
       </c>
       <c r="L122" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N122" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="4" t="inlineStr"/>
       <c r="R122" t="n">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="S122" s="4" t="n">
-        <v>0.7405189620758483</v>
+        <v>0.7880794701986755</v>
       </c>
       <c r="T122" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U122" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="W122" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -23244,7 +23196,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -23259,7 +23211,7 @@
         <v>4</v>
       </c>
       <c r="H123" t="n">
-        <v>-1.917076679237251</v>
+        <v>-2.496658949555008</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -23267,44 +23219,44 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>884</v>
+        <v>274</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0.6481900452488688</v>
+        <v>0.6386861313868614</v>
       </c>
       <c r="L123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M123" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N123" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>0.640625</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="4" t="inlineStr"/>
       <c r="R123" t="n">
-        <v>884</v>
+        <v>274</v>
       </c>
       <c r="S123" s="4" t="n">
-        <v>0.7262443438914027</v>
+        <v>0.7481751824817519</v>
       </c>
       <c r="T123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U123" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="V123" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="W123" s="4" t="n">
-        <v>0.765625</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -23327,7 +23279,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -23342,7 +23294,7 @@
         <v>6</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.917076679237251</v>
+        <v>-2.496658949555008</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -23350,44 +23302,44 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>1095</v>
+        <v>399</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0.6602739726027397</v>
+        <v>0.6365914786967418</v>
       </c>
       <c r="L124" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N124" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.625</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="4" t="inlineStr"/>
       <c r="R124" t="n">
-        <v>1094</v>
+        <v>399</v>
       </c>
       <c r="S124" s="4" t="n">
-        <v>0.7394881170018281</v>
+        <v>0.7443609022556391</v>
       </c>
       <c r="T124" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U124" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="W124" s="4" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="X124" t="n">
         <v>0</v>
@@ -23410,7 +23362,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -23425,7 +23377,7 @@
         <v>2</v>
       </c>
       <c r="H125" t="n">
-        <v>1.663588817688955</v>
+        <v>1.062848019793772</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -23433,44 +23385,44 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0.7172995780590717</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
         <v>3</v>
       </c>
-      <c r="M125" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N125" t="n">
-        <v>9</v>
-      </c>
       <c r="O125" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="4" t="inlineStr"/>
       <c r="R125" t="n">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="S125" s="4" t="n">
-        <v>0.7932489451476793</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="T125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
         <v>3</v>
       </c>
-      <c r="U125" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="V125" t="n">
-        <v>9</v>
-      </c>
       <c r="W125" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
@@ -23493,7 +23445,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -23508,7 +23460,7 @@
         <v>4</v>
       </c>
       <c r="H126" t="n">
-        <v>1.663588817688955</v>
+        <v>1.062848019793772</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -23516,44 +23468,44 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0.6901041666666666</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="L126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="4" t="inlineStr"/>
       <c r="R126" t="n">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="S126" s="4" t="n">
-        <v>0.7786458333333334</v>
+        <v>0.7288135593220338</v>
       </c>
       <c r="T126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U126" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="V126" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W126" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="X126" t="n">
         <v>0</v>
@@ -23576,7 +23528,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -23591,7 +23543,7 @@
         <v>6</v>
       </c>
       <c r="H127" t="n">
-        <v>1.663588817688955</v>
+        <v>1.062848019793772</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -23599,44 +23551,44 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0.6982758620689655</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="L127" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M127" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="N127" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O127" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="4" t="inlineStr"/>
       <c r="R127" t="n">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="S127" s="4" t="n">
-        <v>0.7823275862068966</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="T127" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U127" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="V127" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="W127" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="X127" t="n">
         <v>0</v>
@@ -23674,7 +23626,7 @@
         <v>2</v>
       </c>
       <c r="H128" t="n">
-        <v>-2.153110047846885</v>
+        <v>-2.232854864433809</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -23757,7 +23709,7 @@
         <v>4</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.153110047846885</v>
+        <v>-2.232854864433809</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -23840,7 +23792,7 @@
         <v>6</v>
       </c>
       <c r="H130" t="n">
-        <v>-2.153110047846885</v>
+        <v>-2.232854864433809</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -23923,7 +23875,7 @@
         <v>2</v>
       </c>
       <c r="H131" t="n">
-        <v>-3.764705882352937</v>
+        <v>-3.843137254901963</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -24006,7 +23958,7 @@
         <v>4</v>
       </c>
       <c r="H132" t="n">
-        <v>-3.764705882352937</v>
+        <v>-3.843137254901963</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -24093,7 +24045,7 @@
         <v>6</v>
       </c>
       <c r="H133" t="n">
-        <v>-3.764705882352937</v>
+        <v>-3.843137254901963</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -24180,7 +24132,7 @@
         <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.5672609400324102</v>
+        <v>-0.648298217179899</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -24263,7 +24215,7 @@
         <v>4</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.5672609400324102</v>
+        <v>-0.648298217179899</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -24346,7 +24298,7 @@
         <v>6</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.5672609400324102</v>
+        <v>-0.648298217179899</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -24433,7 +24385,7 @@
         <v>2</v>
       </c>
       <c r="H137" t="n">
-        <v>-6.336091121583898</v>
+        <v>-6.244263392628935</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -24508,7 +24460,7 @@
         <v>4</v>
       </c>
       <c r="H138" t="n">
-        <v>-6.336091121583898</v>
+        <v>-6.244263392628935</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -24587,7 +24539,7 @@
         <v>6</v>
       </c>
       <c r="H139" t="n">
-        <v>-6.336091121583898</v>
+        <v>-6.244263392628935</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -24666,7 +24618,7 @@
         <v>2</v>
       </c>
       <c r="H140" t="n">
-        <v>-7.942237644013339</v>
+        <v>-7.851984574810356</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -24745,7 +24697,7 @@
         <v>4</v>
       </c>
       <c r="H141" t="n">
-        <v>-7.942237644013339</v>
+        <v>-7.851984574810356</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -24824,7 +24776,7 @@
         <v>6</v>
       </c>
       <c r="H142" t="n">
-        <v>-7.942237644013339</v>
+        <v>-7.851984574810356</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -24907,7 +24859,7 @@
         <v>2</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.133900696152303</v>
+        <v>-3.038933552261858</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -24986,7 +24938,7 @@
         <v>4</v>
       </c>
       <c r="H144" t="n">
-        <v>-3.133900696152303</v>
+        <v>-3.038933552261858</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -25069,7 +25021,7 @@
         <v>6</v>
       </c>
       <c r="H145" t="n">
-        <v>-3.133900696152303</v>
+        <v>-3.038933552261858</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -25156,7 +25108,7 @@
         <v>2</v>
       </c>
       <c r="H146" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -25231,7 +25183,7 @@
         <v>4</v>
       </c>
       <c r="H147" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -25310,7 +25262,7 @@
         <v>6</v>
       </c>
       <c r="H148" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -25393,7 +25345,7 @@
         <v>2</v>
       </c>
       <c r="H149" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -25468,7 +25420,7 @@
         <v>4</v>
       </c>
       <c r="H150" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -25543,7 +25495,7 @@
         <v>6</v>
       </c>
       <c r="H151" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -25626,7 +25578,7 @@
         <v>2</v>
       </c>
       <c r="H152" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -25709,7 +25661,7 @@
         <v>4</v>
       </c>
       <c r="H153" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -25792,7 +25744,7 @@
         <v>6</v>
       </c>
       <c r="H154" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -25875,7 +25827,7 @@
         <v>2</v>
       </c>
       <c r="H155" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -25950,7 +25902,7 @@
         <v>4</v>
       </c>
       <c r="H156" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -26033,7 +25985,7 @@
         <v>6</v>
       </c>
       <c r="H157" t="n">
-        <v>-10.31468202204252</v>
+        <v>-10.31468001155295</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -26116,7 +26068,7 @@
         <v>2</v>
       </c>
       <c r="H158" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -26191,7 +26143,7 @@
         <v>4</v>
       </c>
       <c r="H159" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -26270,7 +26222,7 @@
         <v>6</v>
       </c>
       <c r="H160" t="n">
-        <v>-10.70495904805402</v>
+        <v>-10.70495704631334</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -26349,7 +26301,7 @@
         <v>2</v>
       </c>
       <c r="H161" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -26432,7 +26384,7 @@
         <v>4</v>
       </c>
       <c r="H162" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -26515,7 +26467,7 @@
         <v>6</v>
       </c>
       <c r="H163" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000002421052631</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -26598,53 +26550,45 @@
         <v>2</v>
       </c>
       <c r="H164" t="n">
-        <v>-3.83142137055128</v>
+        <v>-4.086851149873604</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0.6826347305389222</v>
+        <v>0.7301587301587301</v>
       </c>
       <c r="L164" t="n">
-        <v>3</v>
-      </c>
-      <c r="M164" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M164" s="4" t="inlineStr"/>
       <c r="N164" t="n">
-        <v>10</v>
-      </c>
-      <c r="O164" s="4" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O164" s="4" t="inlineStr"/>
       <c r="P164" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" t="n">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="S164" s="4" t="n">
-        <v>0.7485029940119761</v>
+        <v>0.8253968253968254</v>
       </c>
       <c r="T164" t="n">
-        <v>3</v>
-      </c>
-      <c r="U164" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U164" s="4" t="inlineStr"/>
       <c r="V164" t="n">
-        <v>10</v>
-      </c>
-      <c r="W164" s="4" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W164" s="4" t="inlineStr"/>
       <c r="X164" t="n">
         <v>0</v>
       </c>
@@ -26681,61 +26625,57 @@
         <v>4</v>
       </c>
       <c r="H165" t="n">
-        <v>-3.83142137055128</v>
+        <v>-4.086851149873604</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>636</v>
+        <v>84</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="L165" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M165" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>1</v>
       </c>
       <c r="P165" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q165" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q165" s="4" t="inlineStr"/>
       <c r="R165" t="n">
-        <v>634</v>
+        <v>84</v>
       </c>
       <c r="S165" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="T165" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U165" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="V165" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="W165" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>1</v>
       </c>
       <c r="X165" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y165" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -26768,7 +26708,7 @@
         <v>6</v>
       </c>
       <c r="H166" t="n">
-        <v>-3.83142137055128</v>
+        <v>-4.086851149873604</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -26855,57 +26795,61 @@
         <v>2</v>
       </c>
       <c r="H167" t="n">
-        <v>-1.761254400705636</v>
+        <v>-2.022182673400785</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>501</v>
+        <v>383</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0.6686626746506986</v>
+        <v>0.6214099216710183</v>
       </c>
       <c r="L167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M167" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N167" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="O167" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q167" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R167" t="n">
-        <v>501</v>
+        <v>383</v>
       </c>
       <c r="S167" s="4" t="n">
-        <v>0.7405189620758483</v>
+        <v>0.7075718015665796</v>
       </c>
       <c r="T167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U167" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="V167" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="W167" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="X167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y167" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y167" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -26938,7 +26882,7 @@
         <v>4</v>
       </c>
       <c r="H168" t="n">
-        <v>-1.761254400705636</v>
+        <v>-2.022182673400785</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -27025,7 +26969,7 @@
         <v>6</v>
       </c>
       <c r="H169" t="n">
-        <v>-1.761254400705636</v>
+        <v>-2.022182673400785</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -27112,7 +27056,7 @@
         <v>2</v>
       </c>
       <c r="H170" t="n">
-        <v>1.619435289738713</v>
+        <v>1.349527693090824</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -27195,7 +27139,7 @@
         <v>4</v>
       </c>
       <c r="H171" t="n">
-        <v>1.619435289738713</v>
+        <v>1.349527693090824</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -27278,7 +27222,7 @@
         <v>6</v>
       </c>
       <c r="H172" t="n">
-        <v>1.619435289738713</v>
+        <v>1.349527693090824</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -27361,7 +27305,7 @@
         <v>2</v>
       </c>
       <c r="H173" t="n">
-        <v>-3.501281286075897</v>
+        <v>-3.928266767110966</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -27448,7 +27392,7 @@
         <v>4</v>
       </c>
       <c r="H174" t="n">
-        <v>-3.501281286075897</v>
+        <v>-3.928266767110966</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -27535,7 +27479,7 @@
         <v>6</v>
       </c>
       <c r="H175" t="n">
-        <v>-3.501281286075897</v>
+        <v>-3.928266767110966</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -27622,7 +27566,7 @@
         <v>2</v>
       </c>
       <c r="H176" t="n">
-        <v>-8.353608526076272</v>
+        <v>-8.759123532598068</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -27701,7 +27645,7 @@
         <v>4</v>
       </c>
       <c r="H177" t="n">
-        <v>-8.353608526076272</v>
+        <v>-8.759123532598068</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -27780,7 +27724,7 @@
         <v>6</v>
       </c>
       <c r="H178" t="n">
-        <v>-8.353608526076272</v>
+        <v>-8.759123532598068</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -27863,27 +27807,27 @@
         <v>2</v>
       </c>
       <c r="H179" t="n">
-        <v>-3.583619927503467</v>
+        <v>-4.01024107826673</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6752767527675276</v>
       </c>
       <c r="L179" t="n">
         <v>7</v>
       </c>
       <c r="M179" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N179" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="O179" s="4" t="n">
         <v>0.5</v>
@@ -27893,10 +27837,10 @@
       </c>
       <c r="Q179" s="4" t="inlineStr"/>
       <c r="R179" t="n">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="S179" s="4" t="n">
-        <v>0.7356687898089171</v>
+        <v>0.7343173431734318</v>
       </c>
       <c r="T179" t="n">
         <v>7</v>
@@ -27905,10 +27849,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="V179" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="W179" s="4" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="X179" t="n">
         <v>0</v>
@@ -27946,52 +27890,52 @@
         <v>4</v>
       </c>
       <c r="H180" t="n">
-        <v>-3.583619927503467</v>
+        <v>-4.01024107826673</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>606</v>
+        <v>444</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>0.6254125412541254</v>
+        <v>0.6644144144144144</v>
       </c>
       <c r="L180" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M180" s="4" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="N180" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="O180" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P180" t="n">
         <v>0</v>
       </c>
       <c r="Q180" s="4" t="inlineStr"/>
       <c r="R180" t="n">
-        <v>605</v>
+        <v>444</v>
       </c>
       <c r="S180" s="4" t="n">
-        <v>0.71900826446281</v>
+        <v>0.7364864864864865</v>
       </c>
       <c r="T180" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="U180" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5</v>
       </c>
       <c r="V180" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="W180" s="4" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="X180" t="n">
         <v>0</v>
@@ -28029,7 +27973,7 @@
         <v>6</v>
       </c>
       <c r="H181" t="n">
-        <v>-3.583619927503467</v>
+        <v>-4.01024107826673</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -28112,7 +28056,7 @@
         <v>2</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.9486834876540229</v>
+        <v>-0.1724855155332494</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -28195,7 +28139,7 @@
         <v>4</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.9486834876540229</v>
+        <v>-0.1724855155332494</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -28278,7 +28222,7 @@
         <v>6</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.9486834876540229</v>
+        <v>-0.1724855155332494</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -28361,48 +28305,52 @@
         <v>2</v>
       </c>
       <c r="H185" t="n">
-        <v>-0.5197041930281254</v>
+        <v>0.2598553988095276</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0.5738396624472574</v>
+        <v>0.6337209302325582</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
-      </c>
-      <c r="M185" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M185" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="N185" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O185" s="4" t="n">
-        <v>0.875</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
       </c>
       <c r="Q185" s="4" t="inlineStr"/>
       <c r="R185" t="n">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="S185" s="4" t="n">
-        <v>0.711864406779661</v>
+        <v>0.7616279069767442</v>
       </c>
       <c r="T185" t="n">
-        <v>0</v>
-      </c>
-      <c r="U185" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U185" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="V185" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W185" s="4" t="n">
-        <v>0.875</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="X185" t="n">
         <v>0</v>
@@ -28440,52 +28388,52 @@
         <v>4</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.5197041930281254</v>
+        <v>0.2598553988095276</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0.59375</v>
+        <v>0.675</v>
       </c>
       <c r="L186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M186" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N186" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O186" s="4" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
       </c>
       <c r="Q186" s="4" t="inlineStr"/>
       <c r="R186" t="n">
-        <v>383</v>
+        <v>279</v>
       </c>
       <c r="S186" s="4" t="n">
-        <v>0.7127937336814621</v>
+        <v>0.7885304659498208</v>
       </c>
       <c r="T186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U186" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V186" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W186" s="4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="X186" t="n">
         <v>0</v>
@@ -28523,52 +28471,52 @@
         <v>6</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.5197041930281254</v>
+        <v>0.2598553988095276</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>452</v>
+        <v>321</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0.6106194690265486</v>
+        <v>0.6822429906542056</v>
       </c>
       <c r="L187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M187" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N187" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O187" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
       </c>
       <c r="Q187" s="4" t="inlineStr"/>
       <c r="R187" t="n">
-        <v>451</v>
+        <v>320</v>
       </c>
       <c r="S187" s="4" t="n">
-        <v>0.7184035476718403</v>
+        <v>0.79375</v>
       </c>
       <c r="T187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U187" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V187" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="W187" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="X187" t="n">
         <v>0</v>
@@ -28606,7 +28554,7 @@
         <v>2</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.161788735313729</v>
+        <v>-0.3872607244504778</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -28685,7 +28633,7 @@
         <v>4</v>
       </c>
       <c r="H189" t="n">
-        <v>-1.161788735313729</v>
+        <v>-0.3872607244504778</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -28768,7 +28716,7 @@
         <v>6</v>
       </c>
       <c r="H190" t="n">
-        <v>-1.161788735313729</v>
+        <v>-0.3872607244504778</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -28851,52 +28799,52 @@
         <v>2</v>
       </c>
       <c r="H191" t="n">
-        <v>2.234636871508378</v>
+        <v>1.955307262569828</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>368</v>
+        <v>650</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0.7445652173913043</v>
+        <v>0.6430769230769231</v>
       </c>
       <c r="L191" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M191" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N191" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="O191" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P191" t="n">
         <v>0</v>
       </c>
       <c r="Q191" s="4" t="inlineStr"/>
       <c r="R191" t="n">
-        <v>368</v>
+        <v>650</v>
       </c>
       <c r="S191" s="4" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.7492307692307693</v>
       </c>
       <c r="T191" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="U191" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="V191" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="W191" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="X191" t="n">
         <v>0</v>
@@ -28934,7 +28882,7 @@
         <v>4</v>
       </c>
       <c r="H192" t="n">
-        <v>2.234636871508378</v>
+        <v>1.955307262569828</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -29017,7 +28965,7 @@
         <v>6</v>
       </c>
       <c r="H193" t="n">
-        <v>2.234636871508378</v>
+        <v>1.955307262569828</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -29100,7 +29048,7 @@
         <v>2</v>
       </c>
       <c r="H194" t="n">
-        <v>-0.2724795640327016</v>
+        <v>-0.544959128065392</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -29183,7 +29131,7 @@
         <v>4</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.2724795640327016</v>
+        <v>-0.544959128065392</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -29266,7 +29214,7 @@
         <v>6</v>
       </c>
       <c r="H196" t="n">
-        <v>-0.2724795640327016</v>
+        <v>-0.544959128065392</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -29349,7 +29297,7 @@
         <v>2</v>
       </c>
       <c r="H197" t="n">
-        <v>3.098591549295771</v>
+        <v>2.8169014084507</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -29432,7 +29380,7 @@
         <v>4</v>
       </c>
       <c r="H198" t="n">
-        <v>3.098591549295771</v>
+        <v>2.8169014084507</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -29515,7 +29463,7 @@
         <v>6</v>
       </c>
       <c r="H199" t="n">
-        <v>3.098591549295771</v>
+        <v>2.8169014084507</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -29598,7 +29546,7 @@
         <v>2</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6156552330694787</v>
+        <v>0.9674582233949014</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -29685,7 +29633,7 @@
         <v>4</v>
       </c>
       <c r="H201" t="n">
-        <v>0.6156552330694787</v>
+        <v>0.9674582233949014</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -29772,7 +29720,7 @@
         <v>6</v>
       </c>
       <c r="H202" t="n">
-        <v>0.6156552330694787</v>
+        <v>0.9674582233949014</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -29859,7 +29807,7 @@
         <v>2</v>
       </c>
       <c r="H203" t="n">
-        <v>-1.633705932932072</v>
+        <v>-1.289767841788481</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -29942,7 +29890,7 @@
         <v>4</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.633705932932072</v>
+        <v>-1.289767841788481</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -30025,7 +29973,7 @@
         <v>6</v>
       </c>
       <c r="H205" t="n">
-        <v>-1.633705932932072</v>
+        <v>-1.289767841788481</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -30108,49 +30056,45 @@
         <v>2</v>
       </c>
       <c r="H206" t="n">
-        <v>9.788867562380045</v>
+        <v>10.17274472168905</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>[8,10)</t>
+          <t>[10,12)</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
       </c>
       <c r="M206" s="4" t="inlineStr"/>
       <c r="N206" t="n">
-        <v>3</v>
-      </c>
-      <c r="O206" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O206" s="4" t="inlineStr"/>
       <c r="P206" t="n">
         <v>0</v>
       </c>
       <c r="Q206" s="4" t="inlineStr"/>
       <c r="R206" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S206" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="T206" t="n">
         <v>0</v>
       </c>
       <c r="U206" s="4" t="inlineStr"/>
       <c r="V206" t="n">
-        <v>3</v>
-      </c>
-      <c r="W206" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W206" s="4" t="inlineStr"/>
       <c r="X206" t="n">
         <v>0</v>
       </c>
@@ -30187,7 +30131,7 @@
         <v>4</v>
       </c>
       <c r="H207" t="n">
-        <v>9.788867562380045</v>
+        <v>10.17274472168905</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -30266,7 +30210,7 @@
         <v>6</v>
       </c>
       <c r="H208" t="n">
-        <v>9.788867562380045</v>
+        <v>10.17274472168905</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -30334,7 +30278,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -30349,7 +30293,7 @@
         <v>2</v>
       </c>
       <c r="H209" t="n">
-        <v>-2.088770886024138</v>
+        <v>-2.349865147125241</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -30360,7 +30304,7 @@
         <v>167</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>0.6826347305389222</v>
+        <v>0.688622754491018</v>
       </c>
       <c r="L209" t="n">
         <v>3</v>
@@ -30369,10 +30313,10 @@
         <v>1</v>
       </c>
       <c r="N209" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O209" s="4" t="n">
-        <v>0.4</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="P209" t="n">
         <v>0</v>
@@ -30382,7 +30326,7 @@
         <v>167</v>
       </c>
       <c r="S209" s="4" t="n">
-        <v>0.7485029940119761</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="T209" t="n">
         <v>3</v>
@@ -30391,10 +30335,10 @@
         <v>1</v>
       </c>
       <c r="V209" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W209" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X209" t="n">
         <v>0</v>
@@ -30417,7 +30361,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -30432,7 +30376,7 @@
         <v>4</v>
       </c>
       <c r="H210" t="n">
-        <v>-2.088770886024138</v>
+        <v>-2.349865147125241</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -30440,53 +30384,49 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>636</v>
+        <v>378</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>0.64937106918239</v>
+        <v>0.6693121693121693</v>
       </c>
       <c r="L210" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M210" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N210" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="O210" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P210" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q210" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q210" s="4" t="inlineStr"/>
       <c r="R210" t="n">
-        <v>634</v>
+        <v>378</v>
       </c>
       <c r="S210" s="4" t="n">
-        <v>0.7208201892744479</v>
+        <v>0.7751322751322751</v>
       </c>
       <c r="T210" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U210" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="V210" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="W210" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="X210" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y210" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -30504,7 +30444,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -30519,7 +30459,7 @@
         <v>6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.088770886024138</v>
+        <v>-2.349865147125241</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -30527,53 +30467,49 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>699</v>
+        <v>447</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>0.6566523605150214</v>
+        <v>0.6756152125279642</v>
       </c>
       <c r="L211" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M211" s="4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N211" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="O211" s="4" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="P211" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q211" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q211" s="4" t="inlineStr"/>
       <c r="R211" t="n">
-        <v>697</v>
+        <v>447</v>
       </c>
       <c r="S211" s="4" t="n">
-        <v>0.7302725968436155</v>
+        <v>0.7740492170022372</v>
       </c>
       <c r="T211" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U211" s="4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="V211" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="W211" s="4" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="X211" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y211" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -30591,7 +30527,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -30606,7 +30542,7 @@
         <v>2</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.3542954839833246</v>
+        <v>-0.6200149711957925</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -30614,53 +30550,49 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>501</v>
+        <v>123</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>0.6686626746506986</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="L212" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M212" s="4" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="O212" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P212" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q212" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q212" s="4" t="inlineStr"/>
       <c r="R212" t="n">
-        <v>501</v>
+        <v>123</v>
       </c>
       <c r="S212" s="4" t="n">
-        <v>0.7405189620758483</v>
+        <v>0.6991869918699187</v>
       </c>
       <c r="T212" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U212" s="4" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="V212" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="W212" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="X212" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y212" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -30678,7 +30610,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -30693,7 +30625,7 @@
         <v>4</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.3542954839833246</v>
+        <v>-0.6200149711957925</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -30701,53 +30633,49 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>884</v>
+        <v>274</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>0.6481900452488688</v>
+        <v>0.6386861313868614</v>
       </c>
       <c r="L213" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M213" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5</v>
       </c>
       <c r="N213" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="O213" s="4" t="n">
-        <v>0.640625</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P213" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q213" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q213" s="4" t="inlineStr"/>
       <c r="R213" t="n">
-        <v>884</v>
+        <v>274</v>
       </c>
       <c r="S213" s="4" t="n">
-        <v>0.7262443438914027</v>
+        <v>0.7481751824817519</v>
       </c>
       <c r="T213" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="U213" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.5</v>
       </c>
       <c r="V213" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="W213" s="4" t="n">
-        <v>0.765625</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="X213" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y213" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -30765,7 +30693,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -30780,7 +30708,7 @@
         <v>6</v>
       </c>
       <c r="H214" t="n">
-        <v>-0.3542954839833246</v>
+        <v>-0.6200149711957925</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -30788,53 +30716,49 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>1095</v>
+        <v>399</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>0.6602739726027397</v>
+        <v>0.6365914786967418</v>
       </c>
       <c r="L214" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M214" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="N214" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="O214" s="4" t="n">
-        <v>0.625</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="P214" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q214" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q214" s="4" t="inlineStr"/>
       <c r="R214" t="n">
-        <v>1094</v>
+        <v>399</v>
       </c>
       <c r="S214" s="4" t="n">
-        <v>0.7394881170018281</v>
+        <v>0.7443609022556391</v>
       </c>
       <c r="T214" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U214" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="V214" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="W214" s="4" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="X214" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y214" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -30852,7 +30776,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -30867,7 +30791,7 @@
         <v>2</v>
       </c>
       <c r="H215" t="n">
-        <v>1.902174282254254</v>
+        <v>1.630437596487089</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -30875,53 +30799,49 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>0.7172995780590717</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N215" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O215" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="P215" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q215" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q215" s="4" t="inlineStr"/>
       <c r="R215" t="n">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="S215" s="4" t="n">
-        <v>0.7932489451476793</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="T215" t="n">
         <v>1</v>
       </c>
       <c r="U215" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V215" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W215" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="X215" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y215" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -30939,7 +30859,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -30954,7 +30874,7 @@
         <v>4</v>
       </c>
       <c r="H216" t="n">
-        <v>1.902174282254254</v>
+        <v>1.630437596487089</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -30962,53 +30882,49 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>0.6901041666666666</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
         <v>3</v>
       </c>
-      <c r="M216" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N216" t="n">
-        <v>13</v>
-      </c>
       <c r="O216" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="P216" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q216" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q216" s="4" t="inlineStr"/>
       <c r="R216" t="n">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="S216" s="4" t="n">
-        <v>0.7786458333333334</v>
+        <v>0.7288135593220338</v>
       </c>
       <c r="T216" t="n">
+        <v>1</v>
+      </c>
+      <c r="U216" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V216" t="n">
         <v>3</v>
       </c>
-      <c r="U216" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="V216" t="n">
-        <v>13</v>
-      </c>
       <c r="W216" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="X216" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y216" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -31026,7 +30942,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>BULLISH_ENGULFING</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -31041,7 +30957,7 @@
         <v>6</v>
       </c>
       <c r="H217" t="n">
-        <v>1.902174282254254</v>
+        <v>1.630437596487089</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -31049,53 +30965,49 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>0.6982758620689655</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="L217" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M217" s="4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="P217" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q217" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q217" s="4" t="inlineStr"/>
       <c r="R217" t="n">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="S217" s="4" t="n">
-        <v>0.7823275862068966</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="T217" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U217" s="4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="V217" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="W217" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="X217" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y217" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -31128,45 +31040,53 @@
         <v>2</v>
       </c>
       <c r="H218" t="n">
-        <v>-4.023602009356075</v>
+        <v>-3.862659439711491</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>[-6,-4)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J218" t="n">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>0.7301587301587301</v>
+        <v>0.6826347305389222</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
-      </c>
-      <c r="M218" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M218" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="N218" t="n">
-        <v>0</v>
-      </c>
-      <c r="O218" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="O218" s="4" t="n">
+        <v>0.4</v>
+      </c>
       <c r="P218" t="n">
         <v>0</v>
       </c>
       <c r="Q218" s="4" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="S218" s="4" t="n">
-        <v>0.8253968253968254</v>
+        <v>0.7485029940119761</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
-      </c>
-      <c r="U218" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U218" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="V218" t="n">
-        <v>0</v>
-      </c>
-      <c r="W218" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="W218" s="4" t="n">
+        <v>0.4</v>
+      </c>
       <c r="X218" t="n">
         <v>0</v>
       </c>
@@ -31203,48 +31123,52 @@
         <v>4</v>
       </c>
       <c r="H219" t="n">
-        <v>-4.023602009356075</v>
+        <v>-3.862659439711491</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>[-8,-4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J219" t="n">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.64937106918239</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M219" s="4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="N219" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>1</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="P219" t="n">
         <v>0</v>
       </c>
       <c r="Q219" s="4" t="inlineStr"/>
       <c r="R219" t="n">
-        <v>84</v>
+        <v>634</v>
       </c>
       <c r="S219" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7208201892744479</v>
       </c>
       <c r="T219" t="n">
-        <v>0</v>
-      </c>
-      <c r="U219" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="U219" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="V219" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="W219" s="4" t="n">
-        <v>1</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="X219" t="n">
         <v>0</v>
@@ -31282,7 +31206,7 @@
         <v>6</v>
       </c>
       <c r="H220" t="n">
-        <v>-4.023602009356075</v>
+        <v>-3.862659439711491</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -31365,7 +31289,7 @@
         <v>2</v>
       </c>
       <c r="H221" t="n">
-        <v>-5.042459770483032</v>
+        <v>-4.88322572074138</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -31448,7 +31372,7 @@
         <v>4</v>
       </c>
       <c r="H222" t="n">
-        <v>-5.042459770483032</v>
+        <v>-4.88322572074138</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -31531,7 +31455,7 @@
         <v>6</v>
       </c>
       <c r="H223" t="n">
-        <v>-5.042459770483032</v>
+        <v>-4.88322572074138</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -31614,7 +31538,7 @@
         <v>2</v>
       </c>
       <c r="H224" t="n">
-        <v>0.9024235264443625</v>
+        <v>1.071626535368431</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -31697,7 +31621,7 @@
         <v>4</v>
       </c>
       <c r="H225" t="n">
-        <v>0.9024235264443625</v>
+        <v>1.071626535368431</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -31780,7 +31704,7 @@
         <v>6</v>
       </c>
       <c r="H226" t="n">
-        <v>0.9024235264443625</v>
+        <v>1.071626535368431</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -31863,61 +31787,57 @@
         <v>2</v>
       </c>
       <c r="H227" t="n">
-        <v>2.074684984762798</v>
+        <v>1.659749315611014</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J227" t="n">
-        <v>678</v>
+        <v>1354</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>0.5737463126843658</v>
+        <v>0.5354505169867061</v>
       </c>
       <c r="L227" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M227" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="N227" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O227" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P227" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q227" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q227" s="4" t="inlineStr"/>
       <c r="R227" t="n">
-        <v>678</v>
+        <v>1353</v>
       </c>
       <c r="S227" s="4" t="n">
-        <v>0.6755162241887905</v>
+        <v>0.6570583887657059</v>
       </c>
       <c r="T227" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="U227" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="V227" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="W227" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="X227" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y227" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -31950,7 +31870,7 @@
         <v>4</v>
       </c>
       <c r="H228" t="n">
-        <v>2.074684984762798</v>
+        <v>1.659749315611014</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -32037,7 +31957,7 @@
         <v>6</v>
       </c>
       <c r="H229" t="n">
-        <v>2.074684984762798</v>
+        <v>1.659749315611014</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -32124,7 +32044,7 @@
         <v>2</v>
       </c>
       <c r="H230" t="n">
-        <v>-2.380951606198034</v>
+        <v>-2.777775022045847</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -32207,7 +32127,7 @@
         <v>4</v>
       </c>
       <c r="H231" t="n">
-        <v>-2.380951606198034</v>
+        <v>-2.777775022045847</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -32290,7 +32210,7 @@
         <v>6</v>
       </c>
       <c r="H232" t="n">
-        <v>-2.380951606198034</v>
+        <v>-2.777775022045847</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -32373,7 +32293,7 @@
         <v>2</v>
       </c>
       <c r="H233" t="n">
-        <v>6.956524064272251</v>
+        <v>6.521743620037901</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -32460,7 +32380,7 @@
         <v>4</v>
       </c>
       <c r="H234" t="n">
-        <v>6.956524064272251</v>
+        <v>6.521743620037901</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -32547,7 +32467,7 @@
         <v>6</v>
       </c>
       <c r="H235" t="n">
-        <v>6.956524064272251</v>
+        <v>6.521743620037901</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46289.78442828055</v>
+        <v>46289.99320143258</v>
       </c>
     </row>
     <row r="4">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>58946</v>
+        <v>58952</v>
       </c>
     </row>
     <row r="22">
